--- a/IA_CCBS_BANK_SIDE/Customer/CCBS_CreateIndividualCustomer.xlsx
+++ b/IA_CCBS_BANK_SIDE/Customer/CCBS_CreateIndividualCustomer.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20399"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sw\Relational_Files\Asset Bank Interfaces_New\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kmilos\source\repos\iApply_CCBS_API\IA_CCBS_BANK_SIDE\Customer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D22364E-B447-4E87-9032-60587B0C69A1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB7C7C3-6937-42B4-B212-0DBEA742F788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11025" activeTab="1" xr2:uid="{71FA6D81-4DAE-49DF-BD64-C0A351CD7C3B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{71FA6D81-4DAE-49DF-BD64-C0A351CD7C3B}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="277">
   <si>
     <t>First Name</t>
   </si>
@@ -810,6 +810,60 @@
   </si>
   <si>
     <t>crp_CBS_updateIdentification</t>
+  </si>
+  <si>
+    <t>AMLFields</t>
+  </si>
+  <si>
+    <t>Class with next fields in extended categories</t>
+  </si>
+  <si>
+    <t>estTransLevel</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>Estimated Transaction Level</t>
+  </si>
+  <si>
+    <t>fundsSD</t>
+  </si>
+  <si>
+    <t>string[]</t>
+  </si>
+  <si>
+    <t>Funds Source / Destination - multiple selection field</t>
+  </si>
+  <si>
+    <t>polExp</t>
+  </si>
+  <si>
+    <t>Political exposure</t>
+  </si>
+  <si>
+    <t>repRisk</t>
+  </si>
+  <si>
+    <t>Reputation Risk</t>
+  </si>
+  <si>
+    <t>busRelPurpose</t>
+  </si>
+  <si>
+    <t>Business Relation Purpose</t>
+  </si>
+  <si>
+    <t>typeOfProduct</t>
+  </si>
+  <si>
+    <t>type of product</t>
+  </si>
+  <si>
+    <t>clientStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client status </t>
   </si>
 </sst>
 </file>
@@ -887,7 +941,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -997,15 +1051,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="5"/>
+      </right>
+      <top style="thin">
+        <color theme="5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1036,7 +1110,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1048,17 +1122,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="20% - Accent4" xfId="1" builtinId="42"/>
@@ -1130,9 +1203,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1170,7 +1243,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1276,7 +1349,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1418,7 +1491,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1427,20 +1500,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89993E1D-86FC-4340-878F-FAF98EE683C1}">
   <dimension ref="B2:C14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="15"/>
       <c r="C2" s="16" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B3" s="16" t="s">
         <v>218</v>
       </c>
@@ -1448,7 +1521,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B4" s="16" t="s">
         <v>220</v>
       </c>
@@ -1456,7 +1529,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B5" s="16" t="s">
         <v>222</v>
       </c>
@@ -1464,11 +1537,11 @@
         <v>223</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B6" s="16"/>
       <c r="C6" s="17"/>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B7" s="16" t="s">
         <v>224</v>
       </c>
@@ -1476,11 +1549,11 @@
         <v>225</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B8" s="16"/>
       <c r="C8" s="17"/>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B9" s="16" t="s">
         <v>226</v>
       </c>
@@ -1488,7 +1561,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B10" s="16" t="s">
         <v>228</v>
       </c>
@@ -1496,15 +1569,15 @@
         <v>229</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B11" s="16"/>
       <c r="C11" s="17"/>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B12" s="16"/>
       <c r="C12" s="17"/>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B13" s="16" t="s">
         <v>230</v>
       </c>
@@ -1512,7 +1585,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B14" s="16"/>
       <c r="C14" s="17"/>
     </row>
@@ -1523,18 +1596,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79128A65-9683-4A44-8F1C-885040A9EB1A}">
-  <dimension ref="A1:G102"/>
-  <sheetFormatPr defaultColWidth="110" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G110"/>
+  <sheetFormatPr defaultColWidth="110" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="87.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="87.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>212</v>
       </c>
@@ -1555,7 +1628,7 @@
       </c>
       <c r="G1" s="12"/>
     </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1573,7 +1646,7 @@
       </c>
       <c r="F2" s="4"/>
     </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1591,7 +1664,7 @@
       </c>
       <c r="F3" s="4"/>
     </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1609,7 +1682,7 @@
       </c>
       <c r="F4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1627,7 +1700,7 @@
       </c>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1645,7 +1718,7 @@
       </c>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1665,7 +1738,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1683,7 +1756,7 @@
       </c>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1703,7 +1776,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1721,7 +1794,7 @@
       </c>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1739,7 +1812,7 @@
       </c>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1757,7 +1830,7 @@
       </c>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1775,7 +1848,7 @@
       </c>
       <c r="F13" s="4"/>
     </row>
-    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1793,7 +1866,7 @@
       </c>
       <c r="F14" s="4"/>
     </row>
-    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1811,7 +1884,7 @@
       </c>
       <c r="F15" s="4"/>
     </row>
-    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1829,7 +1902,7 @@
       </c>
       <c r="F16" s="4"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1847,7 +1920,7 @@
       </c>
       <c r="F17" s="4"/>
     </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1865,7 +1938,7 @@
       </c>
       <c r="F18" s="4"/>
     </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1883,7 +1956,7 @@
       </c>
       <c r="F19" s="4"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1901,7 +1974,7 @@
       </c>
       <c r="F20" s="4"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1919,7 +1992,7 @@
       </c>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1937,7 +2010,7 @@
       </c>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1955,7 +2028,7 @@
       </c>
       <c r="F23" s="4"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1973,7 +2046,7 @@
       </c>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1991,7 +2064,7 @@
       </c>
       <c r="F25" s="4"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -2009,7 +2082,7 @@
       </c>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -2027,7 +2100,7 @@
       </c>
       <c r="F27" s="4"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -2045,7 +2118,7 @@
       </c>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -2065,7 +2138,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -2083,7 +2156,7 @@
       </c>
       <c r="F30" s="4"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>32</v>
       </c>
@@ -2101,7 +2174,7 @@
       </c>
       <c r="F31" s="4"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>33</v>
       </c>
@@ -2119,7 +2192,7 @@
       </c>
       <c r="F32" s="4"/>
     </row>
-    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>35</v>
       </c>
@@ -2137,7 +2210,7 @@
       </c>
       <c r="F33" s="4"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>36</v>
       </c>
@@ -2155,7 +2228,7 @@
       </c>
       <c r="F34" s="4"/>
     </row>
-    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>37</v>
       </c>
@@ -2173,7 +2246,7 @@
       </c>
       <c r="F35" s="4"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>38</v>
       </c>
@@ -2191,7 +2264,7 @@
       </c>
       <c r="F36" s="4"/>
     </row>
-    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>39</v>
       </c>
@@ -2209,7 +2282,7 @@
       </c>
       <c r="F37" s="4"/>
     </row>
-    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>40</v>
       </c>
@@ -2225,7 +2298,7 @@
       </c>
       <c r="F38" s="4"/>
     </row>
-    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>41</v>
       </c>
@@ -2241,7 +2314,7 @@
       </c>
       <c r="F39" s="4"/>
     </row>
-    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>42</v>
       </c>
@@ -2257,7 +2330,7 @@
       </c>
       <c r="F40" s="4"/>
     </row>
-    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>43</v>
       </c>
@@ -2275,7 +2348,7 @@
       </c>
       <c r="F41" s="4"/>
     </row>
-    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>44</v>
       </c>
@@ -2293,7 +2366,7 @@
       </c>
       <c r="F42" s="4"/>
     </row>
-    <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>45</v>
       </c>
@@ -2311,7 +2384,7 @@
       </c>
       <c r="F43" s="4"/>
     </row>
-    <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>46</v>
       </c>
@@ -2329,7 +2402,7 @@
       </c>
       <c r="F44" s="4"/>
     </row>
-    <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>47</v>
       </c>
@@ -2349,7 +2422,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>48</v>
       </c>
@@ -2367,7 +2440,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>49</v>
       </c>
@@ -2387,7 +2460,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>50</v>
       </c>
@@ -2405,7 +2478,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>51</v>
       </c>
@@ -2425,7 +2498,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>52</v>
       </c>
@@ -2443,7 +2516,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>53</v>
       </c>
@@ -2463,7 +2536,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>54</v>
       </c>
@@ -2481,7 +2554,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>55</v>
       </c>
@@ -2501,7 +2574,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>56</v>
       </c>
@@ -2519,7 +2592,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>57</v>
       </c>
@@ -2539,7 +2612,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>58</v>
       </c>
@@ -2557,7 +2630,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>59</v>
       </c>
@@ -2577,7 +2650,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>60</v>
       </c>
@@ -2595,7 +2668,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>61</v>
       </c>
@@ -2615,7 +2688,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>62</v>
       </c>
@@ -2633,7 +2706,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>63</v>
       </c>
@@ -2653,7 +2726,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>64</v>
       </c>
@@ -2671,7 +2744,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>65</v>
       </c>
@@ -2691,7 +2764,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>66</v>
       </c>
@@ -2709,7 +2782,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>67</v>
       </c>
@@ -2729,7 +2802,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>68</v>
       </c>
@@ -2747,7 +2820,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>69</v>
       </c>
@@ -2767,7 +2840,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>70</v>
       </c>
@@ -2785,7 +2858,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="14">
         <v>71</v>
       </c>
@@ -2805,7 +2878,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>72</v>
       </c>
@@ -2825,7 +2898,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>73</v>
       </c>
@@ -2843,7 +2916,7 @@
       </c>
       <c r="F71" s="2"/>
     </row>
-    <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>74</v>
       </c>
@@ -2861,7 +2934,7 @@
       </c>
       <c r="F72" s="8"/>
     </row>
-    <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>75</v>
       </c>
@@ -2877,7 +2950,7 @@
       </c>
       <c r="F73" s="2"/>
     </row>
-    <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>76</v>
       </c>
@@ -2895,7 +2968,7 @@
       </c>
       <c r="F74" s="2"/>
     </row>
-    <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>77</v>
       </c>
@@ -2913,7 +2986,7 @@
       </c>
       <c r="F75" s="2"/>
     </row>
-    <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>78</v>
       </c>
@@ -2931,7 +3004,7 @@
       </c>
       <c r="F76" s="2"/>
     </row>
-    <row r="77" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>79</v>
       </c>
@@ -2949,7 +3022,7 @@
       </c>
       <c r="F77" s="2"/>
     </row>
-    <row r="78" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>80</v>
       </c>
@@ -2967,7 +3040,7 @@
       </c>
       <c r="F78" s="2"/>
     </row>
-    <row r="79" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>81</v>
       </c>
@@ -2985,7 +3058,7 @@
       </c>
       <c r="F79" s="2"/>
     </row>
-    <row r="80" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>82</v>
       </c>
@@ -3003,7 +3076,7 @@
       </c>
       <c r="F80" s="2"/>
     </row>
-    <row r="81" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>83</v>
       </c>
@@ -3021,7 +3094,7 @@
       </c>
       <c r="F81" s="2"/>
     </row>
-    <row r="82" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>84</v>
       </c>
@@ -3039,7 +3112,7 @@
       </c>
       <c r="F82" s="2"/>
     </row>
-    <row r="83" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>85</v>
       </c>
@@ -3057,7 +3130,7 @@
       </c>
       <c r="F83" s="2"/>
     </row>
-    <row r="84" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>86</v>
       </c>
@@ -3075,7 +3148,7 @@
       </c>
       <c r="F84" s="2"/>
     </row>
-    <row r="85" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>87</v>
       </c>
@@ -3093,7 +3166,7 @@
       </c>
       <c r="F85" s="2"/>
     </row>
-    <row r="86" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>88</v>
       </c>
@@ -3111,7 +3184,7 @@
       </c>
       <c r="F86" s="2"/>
     </row>
-    <row r="87" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>89</v>
       </c>
@@ -3129,7 +3202,7 @@
       </c>
       <c r="F87" s="2"/>
     </row>
-    <row r="88" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>90</v>
       </c>
@@ -3147,7 +3220,7 @@
       </c>
       <c r="F88" s="2"/>
     </row>
-    <row r="89" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>91</v>
       </c>
@@ -3165,7 +3238,7 @@
       </c>
       <c r="F89" s="2"/>
     </row>
-    <row r="90" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>92</v>
       </c>
@@ -3183,7 +3256,7 @@
       </c>
       <c r="F90" s="2"/>
     </row>
-    <row r="91" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>93</v>
       </c>
@@ -3201,7 +3274,7 @@
       </c>
       <c r="F91" s="2"/>
     </row>
-    <row r="92" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>94</v>
       </c>
@@ -3219,7 +3292,7 @@
       </c>
       <c r="F92" s="2"/>
     </row>
-    <row r="93" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>95</v>
       </c>
@@ -3237,7 +3310,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>96</v>
       </c>
@@ -3255,7 +3328,7 @@
       </c>
       <c r="F94" s="2"/>
     </row>
-    <row r="95" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>97</v>
       </c>
@@ -3273,7 +3346,7 @@
       </c>
       <c r="F95" s="8"/>
     </row>
-    <row r="96" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>98</v>
       </c>
@@ -3291,7 +3364,7 @@
       </c>
       <c r="F96" s="2"/>
     </row>
-    <row r="97" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>99</v>
       </c>
@@ -3309,7 +3382,7 @@
       </c>
       <c r="F97" s="2"/>
     </row>
-    <row r="98" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>100</v>
       </c>
@@ -3327,7 +3400,7 @@
       </c>
       <c r="F98" s="2"/>
     </row>
-    <row r="99" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>101</v>
       </c>
@@ -3345,7 +3418,7 @@
       </c>
       <c r="F99" s="2"/>
     </row>
-    <row r="100" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>102</v>
       </c>
@@ -3363,7 +3436,7 @@
       </c>
       <c r="F100" s="2"/>
     </row>
-    <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>103</v>
       </c>
@@ -3381,7 +3454,7 @@
       </c>
       <c r="F101" s="2"/>
     </row>
-    <row r="102" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>104</v>
       </c>
@@ -3399,19 +3472,145 @@
       </c>
       <c r="F102" s="2"/>
     </row>
+    <row r="103" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>105</v>
+      </c>
+      <c r="B103" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="C103" s="20"/>
+      <c r="D103" s="20"/>
+      <c r="E103" s="20"/>
+      <c r="F103" s="21" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>106</v>
+      </c>
+      <c r="B104" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="C104" s="20"/>
+      <c r="D104" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="E104" s="20"/>
+      <c r="F104" s="21" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>107</v>
+      </c>
+      <c r="B105" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="C105" s="20"/>
+      <c r="D105" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="E105" s="20"/>
+      <c r="F105" s="21" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>108</v>
+      </c>
+      <c r="B106" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="C106" s="20"/>
+      <c r="D106" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="E106" s="20"/>
+      <c r="F106" s="21" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>109</v>
+      </c>
+      <c r="B107" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="C107" s="20"/>
+      <c r="D107" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="E107" s="20"/>
+      <c r="F107" s="21" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>110</v>
+      </c>
+      <c r="B108" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="C108" s="20"/>
+      <c r="D108" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="E108" s="20"/>
+      <c r="F108" s="21" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>111</v>
+      </c>
+      <c r="B109" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="C109" s="20"/>
+      <c r="D109" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="E109" s="20"/>
+      <c r="F109" s="21" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>112</v>
+      </c>
+      <c r="B110" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="C110" s="20"/>
+      <c r="D110" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="E110" s="20"/>
+      <c r="F110" s="21" t="s">
+        <v>276</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{010E3364-7D39-4334-B684-BC5F9F35E73D}"/>
-  <sortState ref="A2:F108">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F108">
     <sortCondition ref="A1"/>
   </sortState>
   <conditionalFormatting sqref="C1">
     <cfRule type="duplicateValues" dxfId="4" priority="2"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C2:C102">
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3420,417 +3619,417 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{378F3E5F-39A3-4E2C-8F24-A5F65D7FC790}">
   <dimension ref="A1:G78"/>
-  <sheetFormatPr defaultColWidth="110" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="110" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="87.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="87.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:7" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="19" t="s">
         <v>217</v>
       </c>
       <c r="G1" s="12"/>
     </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="22">
+    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="F2" s="20"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="22">
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="F3" s="20"/>
-    </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="22">
-        <v>3</v>
-      </c>
-      <c r="B4" s="18" t="s">
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="F4" s="20"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22">
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="F5" s="20"/>
-    </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22">
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>242</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="22">
+    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>243</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>244</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="18" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="22">
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>245</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="18">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="22">
+    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="F10" s="19"/>
-    </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="22">
+      <c r="F10" s="18"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>250</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="F11" s="19"/>
-    </row>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="22">
+      <c r="F11" s="18"/>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="F12" s="22"/>
-    </row>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="22">
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18" t="s">
+      <c r="B13" s="2"/>
+      <c r="C13" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="F13" s="22"/>
-    </row>
-    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="22">
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19" t="s">
+      <c r="B14" s="18"/>
+      <c r="C14" s="18" t="s">
         <v>254</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="F14" s="22"/>
-    </row>
-    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="22">
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="E15" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F15" s="22"/>
-    </row>
-    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="22">
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18" t="s">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F16" s="22"/>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="22">
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18" t="s">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E17" s="22" t="s">
+      <c r="E17" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F17" s="22"/>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="22">
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18" t="s">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F18" s="22"/>
-    </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="22">
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18" t="s">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22" t="s">
+      <c r="D19" s="1"/>
+      <c r="E19" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F19" s="22"/>
-    </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{639BF047-A3D9-48E7-80C0-18A785A38D06}"/>
-  <sortState ref="A2:F79">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F79">
     <sortCondition ref="A1"/>
   </sortState>
   <conditionalFormatting sqref="C1">
